--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -675,37 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127782134</v>
+        <v>127781134</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>92622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629724</v>
+        <v>629600</v>
       </c>
       <c r="R2" t="n">
-        <v>6918393</v>
+        <v>6918449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,42 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127781134</v>
+        <v>127782134</v>
       </c>
       <c r="B3" t="n">
-        <v>92622</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629600</v>
+        <v>629724</v>
       </c>
       <c r="R3" t="n">
-        <v>6918449</v>
+        <v>6918393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127780507</v>
+        <v>127780867</v>
       </c>
       <c r="B4" t="n">
         <v>98450</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629653</v>
+        <v>629672</v>
       </c>
       <c r="R4" t="n">
-        <v>6918484</v>
+        <v>6918466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127780596</v>
+        <v>127780507</v>
       </c>
       <c r="B5" t="n">
         <v>98450</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629700</v>
+        <v>629653</v>
       </c>
       <c r="R5" t="n">
-        <v>6918458</v>
+        <v>6918484</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,7 +1089,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127780867</v>
+        <v>127780596</v>
       </c>
       <c r="B6" t="n">
         <v>98450</v>
@@ -1124,7 +1119,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629672</v>
+        <v>629700</v>
       </c>
       <c r="R6" t="n">
-        <v>6918466</v>
+        <v>6918458</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127780189</v>
+        <v>127780169</v>
       </c>
       <c r="B8" t="n">
         <v>98450</v>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629736</v>
+        <v>629748</v>
       </c>
       <c r="R8" t="n">
-        <v>6918427</v>
+        <v>6918443</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127780169</v>
+        <v>127780189</v>
       </c>
       <c r="B9" t="n">
         <v>98450</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629748</v>
+        <v>629736</v>
       </c>
       <c r="R9" t="n">
-        <v>6918443</v>
+        <v>6918427</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127782245</v>
+        <v>127780755</v>
       </c>
       <c r="B12" t="n">
         <v>98450</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629718</v>
+        <v>629653</v>
       </c>
       <c r="R12" t="n">
-        <v>6918363</v>
+        <v>6918437</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,7 +1811,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127780755</v>
+        <v>127782245</v>
       </c>
       <c r="B13" t="n">
         <v>98450</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629653</v>
+        <v>629718</v>
       </c>
       <c r="R13" t="n">
-        <v>6918437</v>
+        <v>6918363</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2119,7 +2119,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127780373</v>
+        <v>127780922</v>
       </c>
       <c r="B16" t="n">
         <v>98450</v>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>629677</v>
+        <v>629663</v>
       </c>
       <c r="R16" t="n">
-        <v>6918415</v>
+        <v>6918462</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127780922</v>
+        <v>127780373</v>
       </c>
       <c r="B17" t="n">
         <v>98450</v>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629663</v>
+        <v>629677</v>
       </c>
       <c r="R17" t="n">
-        <v>6918462</v>
+        <v>6918415</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127780756</v>
+        <v>127782007</v>
       </c>
       <c r="B18" t="n">
-        <v>92622</v>
+        <v>98484</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,31 +2332,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2365,10 +2360,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629700</v>
+        <v>629724</v>
       </c>
       <c r="R18" t="n">
-        <v>6918458</v>
+        <v>6918393</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2524,10 +2519,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127782007</v>
+        <v>127780756</v>
       </c>
       <c r="B20" t="n">
-        <v>98484</v>
+        <v>92622</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,26 +2530,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629724</v>
+        <v>629700</v>
       </c>
       <c r="R20" t="n">
-        <v>6918393</v>
+        <v>6918458</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127781080</v>
+        <v>127780668</v>
       </c>
       <c r="B21" t="n">
         <v>98450</v>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629647</v>
+        <v>629662</v>
       </c>
       <c r="R21" t="n">
-        <v>6918478</v>
+        <v>6918438</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127780668</v>
+        <v>127780876</v>
       </c>
       <c r="B22" t="n">
         <v>98450</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629662</v>
+        <v>629673</v>
       </c>
       <c r="R22" t="n">
-        <v>6918438</v>
+        <v>6918486</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127780876</v>
+        <v>127782100</v>
       </c>
       <c r="B23" t="n">
         <v>98450</v>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629673</v>
+        <v>629721</v>
       </c>
       <c r="R23" t="n">
-        <v>6918486</v>
+        <v>6918403</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127782100</v>
+        <v>127781080</v>
       </c>
       <c r="B24" t="n">
         <v>98450</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629721</v>
+        <v>629647</v>
       </c>
       <c r="R24" t="n">
-        <v>6918403</v>
+        <v>6918478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127780500</v>
+        <v>127781736</v>
       </c>
       <c r="B30" t="n">
         <v>98450</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3581,7 +3581,7 @@
         <v>629667</v>
       </c>
       <c r="R30" t="n">
-        <v>6918457</v>
+        <v>6918408</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127781736</v>
+        <v>127780500</v>
       </c>
       <c r="B31" t="n">
         <v>98450</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3682,7 +3682,7 @@
         <v>629667</v>
       </c>
       <c r="R31" t="n">
-        <v>6918408</v>
+        <v>6918457</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127781134</v>
+        <v>127780867</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629600</v>
+        <v>629672</v>
       </c>
       <c r="R2" t="n">
-        <v>6918449</v>
+        <v>6918466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +779,7 @@
         <v>127782134</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127780867</v>
+        <v>127780507</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,7 +907,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629672</v>
+        <v>629653</v>
       </c>
       <c r="R4" t="n">
-        <v>6918466</v>
+        <v>6918484</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127780507</v>
+        <v>127780596</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,7 +1008,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1027,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629653</v>
+        <v>629700</v>
       </c>
       <c r="R5" t="n">
-        <v>6918484</v>
+        <v>6918458</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,6 +1053,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,37 +1084,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127780596</v>
+        <v>127781134</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>92628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629700</v>
+        <v>629600</v>
       </c>
       <c r="R6" t="n">
-        <v>6918458</v>
+        <v>6918449</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,7 +1198,7 @@
         <v>127781923</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127780169</v>
+        <v>127780189</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629748</v>
+        <v>629736</v>
       </c>
       <c r="R8" t="n">
-        <v>6918443</v>
+        <v>6918427</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127780189</v>
+        <v>127780169</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629736</v>
+        <v>629748</v>
       </c>
       <c r="R9" t="n">
-        <v>6918427</v>
+        <v>6918443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,37 +1498,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127781967</v>
+        <v>127781223</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>92622</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1537,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629682</v>
+        <v>629600</v>
       </c>
       <c r="R10" t="n">
-        <v>6918424</v>
+        <v>6918449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,11 +1578,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Kan finnas mer runt om i blåbärsriset</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,42 +1604,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127781223</v>
+        <v>127781967</v>
       </c>
       <c r="B11" t="n">
-        <v>92616</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629600</v>
+        <v>629682</v>
       </c>
       <c r="R11" t="n">
-        <v>6918449</v>
+        <v>6918424</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,6 +1679,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kan finnas mer runt om i blåbärsriset</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,7 +1713,7 @@
         <v>127780755</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>127782245</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>127780499</v>
       </c>
       <c r="B14" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>127781874</v>
       </c>
       <c r="B15" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>127780922</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>127780373</v>
       </c>
       <c r="B17" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127782007</v>
+        <v>127780806</v>
       </c>
       <c r="B18" t="n">
-        <v>98484</v>
+        <v>97333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,38 +2332,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629724</v>
+        <v>629705</v>
       </c>
       <c r="R18" t="n">
-        <v>6918393</v>
+        <v>6918478</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127780806</v>
+        <v>127782007</v>
       </c>
       <c r="B19" t="n">
-        <v>97327</v>
+        <v>98490</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,34 +2429,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629705</v>
+        <v>629724</v>
       </c>
       <c r="R19" t="n">
-        <v>6918478</v>
+        <v>6918393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
         <v>127780756</v>
       </c>
       <c r="B20" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127780668</v>
+        <v>127781080</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629662</v>
+        <v>629647</v>
       </c>
       <c r="R21" t="n">
-        <v>6918438</v>
+        <v>6918478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
         <v>127780876</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782100</v>
+        <v>127780668</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629721</v>
+        <v>629662</v>
       </c>
       <c r="R23" t="n">
-        <v>6918403</v>
+        <v>6918438</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127781080</v>
+        <v>127782100</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629647</v>
+        <v>629721</v>
       </c>
       <c r="R24" t="n">
-        <v>6918478</v>
+        <v>6918403</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,7 +3032,7 @@
         <v>127781827</v>
       </c>
       <c r="B25" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>127781136</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>127780720</v>
       </c>
       <c r="B27" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>127781281</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>127780808</v>
       </c>
       <c r="B29" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,10 +3539,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127781736</v>
+        <v>127780881</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3581,7 +3581,7 @@
         <v>629667</v>
       </c>
       <c r="R30" t="n">
-        <v>6918408</v>
+        <v>6918457</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127780500</v>
+        <v>127781736</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3682,7 +3682,7 @@
         <v>629667</v>
       </c>
       <c r="R31" t="n">
-        <v>6918457</v>
+        <v>6918408</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127780867</v>
+        <v>127782134</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629672</v>
+        <v>629724</v>
       </c>
       <c r="R2" t="n">
-        <v>6918466</v>
+        <v>6918393</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127782134</v>
+        <v>127780867</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629724</v>
+        <v>629672</v>
       </c>
       <c r="R3" t="n">
-        <v>6918393</v>
+        <v>6918466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
         <v>127780507</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127780596</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>127781134</v>
       </c>
       <c r="B6" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>127781923</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127780189</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>127780169</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>127781223</v>
       </c>
       <c r="B10" t="n">
-        <v>92622</v>
+        <v>92625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>127781967</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>127780755</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>127782245</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>127780499</v>
       </c>
       <c r="B14" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>127781874</v>
       </c>
       <c r="B15" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>127780922</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>127780373</v>
       </c>
       <c r="B17" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127780806</v>
+        <v>127782007</v>
       </c>
       <c r="B18" t="n">
-        <v>97333</v>
+        <v>98493</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,34 +2332,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629705</v>
+        <v>629724</v>
       </c>
       <c r="R18" t="n">
-        <v>6918478</v>
+        <v>6918393</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2422,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127782007</v>
+        <v>127780756</v>
       </c>
       <c r="B19" t="n">
-        <v>98490</v>
+        <v>92631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,26 +2433,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2457,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629724</v>
+        <v>629700</v>
       </c>
       <c r="R19" t="n">
-        <v>6918393</v>
+        <v>6918458</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127780756</v>
+        <v>127780806</v>
       </c>
       <c r="B20" t="n">
-        <v>92628</v>
+        <v>97336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,43 +2539,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629700</v>
+        <v>629705</v>
       </c>
       <c r="R20" t="n">
-        <v>6918458</v>
+        <v>6918478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127781080</v>
+        <v>127780876</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629647</v>
+        <v>629673</v>
       </c>
       <c r="R21" t="n">
-        <v>6918478</v>
+        <v>6918486</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127780876</v>
+        <v>127780668</v>
       </c>
       <c r="B22" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629673</v>
+        <v>629662</v>
       </c>
       <c r="R22" t="n">
-        <v>6918486</v>
+        <v>6918438</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127780668</v>
+        <v>127782100</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629662</v>
+        <v>629721</v>
       </c>
       <c r="R23" t="n">
-        <v>6918438</v>
+        <v>6918403</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127782100</v>
+        <v>127781080</v>
       </c>
       <c r="B24" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629721</v>
+        <v>629647</v>
       </c>
       <c r="R24" t="n">
-        <v>6918403</v>
+        <v>6918478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,7 +3032,7 @@
         <v>127781827</v>
       </c>
       <c r="B25" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>127781136</v>
       </c>
       <c r="B26" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>127780720</v>
       </c>
       <c r="B27" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>127781281</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>127780808</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>127780881</v>
       </c>
       <c r="B30" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>127781736</v>
       </c>
       <c r="B31" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -675,37 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127782134</v>
+        <v>127781134</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>92639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629724</v>
+        <v>629600</v>
       </c>
       <c r="R2" t="n">
-        <v>6918393</v>
+        <v>6918449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +789,7 @@
         <v>127780867</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127780507</v>
+        <v>127782134</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -916,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629653</v>
+        <v>629724</v>
       </c>
       <c r="R4" t="n">
-        <v>6918484</v>
+        <v>6918393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127780596</v>
+        <v>127780507</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1008,7 +1018,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1017,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629700</v>
+        <v>629653</v>
       </c>
       <c r="R5" t="n">
-        <v>6918458</v>
+        <v>6918484</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,42 +1089,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127781134</v>
+        <v>127780596</v>
       </c>
       <c r="B6" t="n">
-        <v>92631</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629600</v>
+        <v>629700</v>
       </c>
       <c r="R6" t="n">
-        <v>6918449</v>
+        <v>6918458</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,7 +1198,7 @@
         <v>127781923</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127780189</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>127780169</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>127781223</v>
       </c>
       <c r="B10" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>127781967</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>127780755</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>127782245</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>127780499</v>
       </c>
       <c r="B14" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>127781874</v>
       </c>
       <c r="B15" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>127780922</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>127780373</v>
       </c>
       <c r="B17" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127782007</v>
+        <v>127780756</v>
       </c>
       <c r="B18" t="n">
-        <v>98493</v>
+        <v>92639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,26 +2332,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2360,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629724</v>
+        <v>629700</v>
       </c>
       <c r="R18" t="n">
-        <v>6918393</v>
+        <v>6918458</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127780756</v>
+        <v>127782007</v>
       </c>
       <c r="B19" t="n">
-        <v>92631</v>
+        <v>98501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,31 +2438,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>219874</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629700</v>
+        <v>629724</v>
       </c>
       <c r="R19" t="n">
-        <v>6918458</v>
+        <v>6918393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
         <v>127780806</v>
       </c>
       <c r="B20" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127780876</v>
+        <v>127782100</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629673</v>
+        <v>629721</v>
       </c>
       <c r="R21" t="n">
-        <v>6918486</v>
+        <v>6918403</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127780668</v>
+        <v>127781080</v>
       </c>
       <c r="B22" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629662</v>
+        <v>629647</v>
       </c>
       <c r="R22" t="n">
-        <v>6918438</v>
+        <v>6918478</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782100</v>
+        <v>127780668</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629721</v>
+        <v>629662</v>
       </c>
       <c r="R23" t="n">
-        <v>6918403</v>
+        <v>6918438</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127781080</v>
+        <v>127780876</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629647</v>
+        <v>629673</v>
       </c>
       <c r="R24" t="n">
-        <v>6918478</v>
+        <v>6918486</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,7 +3032,7 @@
         <v>127781827</v>
       </c>
       <c r="B25" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>127781136</v>
       </c>
       <c r="B26" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>127780720</v>
       </c>
       <c r="B27" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>127781281</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>127780808</v>
       </c>
       <c r="B29" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>127780881</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>127781736</v>
       </c>
       <c r="B31" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127781134</v>
       </c>
       <c r="B2" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127780867</v>
+        <v>127782134</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629672</v>
+        <v>629724</v>
       </c>
       <c r="R3" t="n">
-        <v>6918466</v>
+        <v>6918393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127782134</v>
+        <v>127780867</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629724</v>
+        <v>629672</v>
       </c>
       <c r="R4" t="n">
-        <v>6918393</v>
+        <v>6918466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
         <v>127780507</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>127780596</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>127781923</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127780189</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>127780169</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>127781223</v>
       </c>
       <c r="B10" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>127781967</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>127780755</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>127782245</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>127780499</v>
       </c>
       <c r="B14" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>127781874</v>
       </c>
       <c r="B15" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>127780922</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>127780373</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127780756</v>
+        <v>127782007</v>
       </c>
       <c r="B18" t="n">
-        <v>92639</v>
+        <v>98502</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,31 +2332,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2365,10 +2360,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629700</v>
+        <v>629724</v>
       </c>
       <c r="R18" t="n">
-        <v>6918458</v>
+        <v>6918393</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,10 +2422,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127782007</v>
+        <v>127780806</v>
       </c>
       <c r="B19" t="n">
-        <v>98501</v>
+        <v>97345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,38 +2433,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629724</v>
+        <v>629705</v>
       </c>
       <c r="R19" t="n">
-        <v>6918393</v>
+        <v>6918478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,10 +2519,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127780806</v>
+        <v>127780756</v>
       </c>
       <c r="B20" t="n">
-        <v>97344</v>
+        <v>92640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,34 +2530,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629705</v>
+        <v>629700</v>
       </c>
       <c r="R20" t="n">
-        <v>6918478</v>
+        <v>6918458</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127782100</v>
+        <v>127780668</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629721</v>
+        <v>629662</v>
       </c>
       <c r="R21" t="n">
-        <v>6918403</v>
+        <v>6918438</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127781080</v>
+        <v>127780876</v>
       </c>
       <c r="B22" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629647</v>
+        <v>629673</v>
       </c>
       <c r="R22" t="n">
-        <v>6918478</v>
+        <v>6918486</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127780668</v>
+        <v>127782100</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629662</v>
+        <v>629721</v>
       </c>
       <c r="R23" t="n">
-        <v>6918438</v>
+        <v>6918403</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127780876</v>
+        <v>127781080</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629673</v>
+        <v>629647</v>
       </c>
       <c r="R24" t="n">
-        <v>6918486</v>
+        <v>6918478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,7 +3032,7 @@
         <v>127781827</v>
       </c>
       <c r="B25" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>127781136</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>127780720</v>
       </c>
       <c r="B27" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>127781281</v>
       </c>
       <c r="B28" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>127780808</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>127780881</v>
       </c>
       <c r="B30" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>127781736</v>
       </c>
       <c r="B31" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127782134</v>
+        <v>127780507</v>
       </c>
       <c r="B3" t="n">
         <v>98468</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629724</v>
+        <v>629653</v>
       </c>
       <c r="R3" t="n">
-        <v>6918393</v>
+        <v>6918484</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127780867</v>
+        <v>127782134</v>
       </c>
       <c r="B4" t="n">
         <v>98468</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629672</v>
+        <v>629724</v>
       </c>
       <c r="R4" t="n">
-        <v>6918466</v>
+        <v>6918393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127780507</v>
+        <v>127780867</v>
       </c>
       <c r="B5" t="n">
         <v>98468</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629653</v>
+        <v>629672</v>
       </c>
       <c r="R5" t="n">
-        <v>6918484</v>
+        <v>6918466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127782007</v>
+        <v>127780806</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>97345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,38 +2332,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629724</v>
+        <v>629705</v>
       </c>
       <c r="R18" t="n">
-        <v>6918393</v>
+        <v>6918478</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127780806</v>
+        <v>127782007</v>
       </c>
       <c r="B19" t="n">
-        <v>97345</v>
+        <v>98502</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,34 +2429,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629705</v>
+        <v>629724</v>
       </c>
       <c r="R19" t="n">
-        <v>6918478</v>
+        <v>6918393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127780881</v>
+        <v>127781736</v>
       </c>
       <c r="B30" t="n">
         <v>98468</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3581,7 +3581,7 @@
         <v>629667</v>
       </c>
       <c r="R30" t="n">
-        <v>6918457</v>
+        <v>6918408</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127781736</v>
+        <v>127780500</v>
       </c>
       <c r="B31" t="n">
         <v>98468</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3682,7 +3682,7 @@
         <v>629667</v>
       </c>
       <c r="R31" t="n">
-        <v>6918408</v>
+        <v>6918457</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127781134</v>
       </c>
       <c r="B2" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127780507</v>
+        <v>127780867</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629653</v>
+        <v>629672</v>
       </c>
       <c r="R3" t="n">
-        <v>6918484</v>
+        <v>6918466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>127782134</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,10 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127780867</v>
+        <v>127780507</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629672</v>
+        <v>629653</v>
       </c>
       <c r="R5" t="n">
-        <v>6918466</v>
+        <v>6918484</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1092,7 @@
         <v>127780596</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>127781923</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127780189</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>127780169</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>127781223</v>
       </c>
       <c r="B10" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>127781967</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>127780755</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>127782245</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>127780499</v>
       </c>
       <c r="B14" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>127781874</v>
       </c>
       <c r="B15" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>127780922</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>127780373</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127780806</v>
+        <v>127782007</v>
       </c>
       <c r="B18" t="n">
-        <v>97345</v>
+        <v>98503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,34 +2332,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629705</v>
+        <v>629724</v>
       </c>
       <c r="R18" t="n">
-        <v>6918478</v>
+        <v>6918393</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2422,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127782007</v>
+        <v>127780806</v>
       </c>
       <c r="B19" t="n">
-        <v>98502</v>
+        <v>97346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,38 +2433,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629724</v>
+        <v>629705</v>
       </c>
       <c r="R19" t="n">
-        <v>6918393</v>
+        <v>6918478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
         <v>127780756</v>
       </c>
       <c r="B20" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127780668</v>
+        <v>127782100</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629662</v>
+        <v>629721</v>
       </c>
       <c r="R21" t="n">
-        <v>6918438</v>
+        <v>6918403</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
         <v>127780876</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782100</v>
+        <v>127781080</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629721</v>
+        <v>629647</v>
       </c>
       <c r="R23" t="n">
-        <v>6918403</v>
+        <v>6918478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127781080</v>
+        <v>127780668</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629647</v>
+        <v>629662</v>
       </c>
       <c r="R24" t="n">
-        <v>6918478</v>
+        <v>6918438</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,7 +3032,7 @@
         <v>127781827</v>
       </c>
       <c r="B25" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>127781136</v>
       </c>
       <c r="B26" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>127780720</v>
       </c>
       <c r="B27" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>127781281</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>127780808</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,10 +3539,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127781736</v>
+        <v>127780881</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3581,7 +3581,7 @@
         <v>629667</v>
       </c>
       <c r="R30" t="n">
-        <v>6918408</v>
+        <v>6918457</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127780500</v>
+        <v>127781736</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3682,7 +3682,7 @@
         <v>629667</v>
       </c>
       <c r="R31" t="n">
-        <v>6918457</v>
+        <v>6918408</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127781134</v>
       </c>
       <c r="B2" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127780867</v>
+        <v>127782134</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629672</v>
+        <v>629724</v>
       </c>
       <c r="R3" t="n">
-        <v>6918466</v>
+        <v>6918393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127782134</v>
+        <v>127780867</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629724</v>
+        <v>629672</v>
       </c>
       <c r="R4" t="n">
-        <v>6918393</v>
+        <v>6918466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
         <v>127780507</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>127780596</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>127781923</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127780189</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>127780169</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>127781223</v>
       </c>
       <c r="B10" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>127781967</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>127780755</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>127782245</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>127780499</v>
       </c>
       <c r="B14" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>127781874</v>
       </c>
       <c r="B15" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>127780922</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>127780373</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127782007</v>
+        <v>127780756</v>
       </c>
       <c r="B18" t="n">
-        <v>98503</v>
+        <v>92642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,26 +2332,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2360,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629724</v>
+        <v>629700</v>
       </c>
       <c r="R18" t="n">
-        <v>6918393</v>
+        <v>6918458</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127780806</v>
+        <v>127782007</v>
       </c>
       <c r="B19" t="n">
-        <v>97346</v>
+        <v>98504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,34 +2438,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629705</v>
+        <v>629724</v>
       </c>
       <c r="R19" t="n">
-        <v>6918478</v>
+        <v>6918393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2519,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127780756</v>
+        <v>127780806</v>
       </c>
       <c r="B20" t="n">
-        <v>92641</v>
+        <v>97347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,43 +2539,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629700</v>
+        <v>629705</v>
       </c>
       <c r="R20" t="n">
-        <v>6918458</v>
+        <v>6918478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127782100</v>
+        <v>127780668</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629721</v>
+        <v>629662</v>
       </c>
       <c r="R21" t="n">
-        <v>6918403</v>
+        <v>6918438</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
         <v>127780876</v>
       </c>
       <c r="B22" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127781080</v>
+        <v>127782100</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629647</v>
+        <v>629721</v>
       </c>
       <c r="R23" t="n">
-        <v>6918478</v>
+        <v>6918403</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127780668</v>
+        <v>127781080</v>
       </c>
       <c r="B24" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629662</v>
+        <v>629647</v>
       </c>
       <c r="R24" t="n">
-        <v>6918438</v>
+        <v>6918478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,7 +3032,7 @@
         <v>127781827</v>
       </c>
       <c r="B25" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>127781136</v>
       </c>
       <c r="B26" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>127780720</v>
       </c>
       <c r="B27" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>127781281</v>
       </c>
       <c r="B28" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>127780808</v>
       </c>
       <c r="B29" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>127780881</v>
       </c>
       <c r="B30" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>127781736</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127781134</v>
+        <v>127782134</v>
       </c>
       <c r="B2" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629600</v>
+        <v>629724</v>
       </c>
       <c r="R2" t="n">
-        <v>6918449</v>
+        <v>6918393</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127782134</v>
+        <v>127780507</v>
       </c>
       <c r="B3" t="n">
         <v>98470</v>
@@ -816,7 +806,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629724</v>
+        <v>629653</v>
       </c>
       <c r="R3" t="n">
-        <v>6918393</v>
+        <v>6918484</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127780867</v>
+        <v>127780596</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -917,7 +907,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629672</v>
+        <v>629700</v>
       </c>
       <c r="R4" t="n">
-        <v>6918466</v>
+        <v>6918458</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,6 +952,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,32 +983,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127780507</v>
+        <v>127781134</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1021,16 +1016,21 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629653</v>
+        <v>629600</v>
       </c>
       <c r="R5" t="n">
-        <v>6918484</v>
+        <v>6918449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,6 +1063,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,7 +1094,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127780596</v>
+        <v>127780867</v>
       </c>
       <c r="B6" t="n">
         <v>98470</v>
@@ -1119,7 +1124,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629700</v>
+        <v>629672</v>
       </c>
       <c r="R6" t="n">
-        <v>6918458</v>
+        <v>6918466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2427,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127782007</v>
+        <v>127780806</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>97347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,38 +2438,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629724</v>
+        <v>629705</v>
       </c>
       <c r="R19" t="n">
-        <v>6918393</v>
+        <v>6918478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127780806</v>
+        <v>127782007</v>
       </c>
       <c r="B20" t="n">
-        <v>97347</v>
+        <v>98504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,34 +2535,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629705</v>
+        <v>629724</v>
       </c>
       <c r="R20" t="n">
-        <v>6918478</v>
+        <v>6918393</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -3539,7 +3539,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127780881</v>
+        <v>127780500</v>
       </c>
       <c r="B30" t="n">
         <v>98470</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -675,37 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127782134</v>
+        <v>127781134</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629724</v>
+        <v>629600</v>
       </c>
       <c r="R2" t="n">
-        <v>6918393</v>
+        <v>6918449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127780507</v>
+        <v>127780867</v>
       </c>
       <c r="B3" t="n">
         <v>98470</v>
@@ -806,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629653</v>
+        <v>629672</v>
       </c>
       <c r="R3" t="n">
-        <v>6918484</v>
+        <v>6918466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127780596</v>
+        <v>127780507</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -907,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -916,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629700</v>
+        <v>629653</v>
       </c>
       <c r="R4" t="n">
-        <v>6918458</v>
+        <v>6918484</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,11 +962,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,42 +988,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127781134</v>
+        <v>127780596</v>
       </c>
       <c r="B5" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629600</v>
+        <v>629700</v>
       </c>
       <c r="R5" t="n">
-        <v>6918449</v>
+        <v>6918458</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,7 +1094,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127780867</v>
+        <v>127782134</v>
       </c>
       <c r="B6" t="n">
         <v>98470</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629672</v>
+        <v>629724</v>
       </c>
       <c r="R6" t="n">
-        <v>6918466</v>
+        <v>6918393</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127780500</v>
+        <v>127780881</v>
       </c>
       <c r="B30" t="n">
         <v>98470</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127781134</v>
+        <v>127782134</v>
       </c>
       <c r="B2" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629600</v>
+        <v>629724</v>
       </c>
       <c r="R2" t="n">
-        <v>6918449</v>
+        <v>6918393</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127780867</v>
+        <v>127780507</v>
       </c>
       <c r="B3" t="n">
         <v>98470</v>
@@ -816,7 +806,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629672</v>
+        <v>629653</v>
       </c>
       <c r="R3" t="n">
-        <v>6918466</v>
+        <v>6918484</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127780507</v>
+        <v>127780596</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -917,7 +907,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629653</v>
+        <v>629700</v>
       </c>
       <c r="R4" t="n">
-        <v>6918484</v>
+        <v>6918458</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,6 +952,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,37 +983,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127780596</v>
+        <v>127781134</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629700</v>
+        <v>629600</v>
       </c>
       <c r="R5" t="n">
-        <v>6918458</v>
+        <v>6918449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,7 +1094,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127782134</v>
+        <v>127780867</v>
       </c>
       <c r="B6" t="n">
         <v>98470</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629724</v>
+        <v>629672</v>
       </c>
       <c r="R6" t="n">
-        <v>6918393</v>
+        <v>6918466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -675,37 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127782134</v>
+        <v>127781134</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629724</v>
+        <v>629600</v>
       </c>
       <c r="R2" t="n">
-        <v>6918393</v>
+        <v>6918449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127780507</v>
+        <v>127780867</v>
       </c>
       <c r="B3" t="n">
         <v>98470</v>
@@ -806,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629653</v>
+        <v>629672</v>
       </c>
       <c r="R3" t="n">
-        <v>6918484</v>
+        <v>6918466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127780596</v>
+        <v>127780507</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -907,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -916,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629700</v>
+        <v>629653</v>
       </c>
       <c r="R4" t="n">
-        <v>6918458</v>
+        <v>6918484</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,11 +962,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,42 +988,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127781134</v>
+        <v>127780596</v>
       </c>
       <c r="B5" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629600</v>
+        <v>629700</v>
       </c>
       <c r="R5" t="n">
-        <v>6918449</v>
+        <v>6918458</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,7 +1094,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127780867</v>
+        <v>127782134</v>
       </c>
       <c r="B6" t="n">
         <v>98470</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629672</v>
+        <v>629724</v>
       </c>
       <c r="R6" t="n">
-        <v>6918466</v>
+        <v>6918393</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127780756</v>
+        <v>127782007</v>
       </c>
       <c r="B18" t="n">
-        <v>92642</v>
+        <v>98504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,31 +2332,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>219874</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2365,10 +2360,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629700</v>
+        <v>629724</v>
       </c>
       <c r="R18" t="n">
-        <v>6918458</v>
+        <v>6918393</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,10 +2422,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127780806</v>
+        <v>127780756</v>
       </c>
       <c r="B19" t="n">
-        <v>97347</v>
+        <v>92642</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,34 +2433,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629705</v>
+        <v>629700</v>
       </c>
       <c r="R19" t="n">
-        <v>6918478</v>
+        <v>6918458</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127782007</v>
+        <v>127780806</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>97347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,38 +2539,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629724</v>
+        <v>629705</v>
       </c>
       <c r="R20" t="n">
-        <v>6918393</v>
+        <v>6918478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127781134</v>
+        <v>127782134</v>
       </c>
       <c r="B2" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629600</v>
+        <v>629724</v>
       </c>
       <c r="R2" t="n">
-        <v>6918449</v>
+        <v>6918393</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,11 +750,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127780867</v>
+        <v>127780507</v>
       </c>
       <c r="B3" t="n">
         <v>98470</v>
@@ -816,7 +806,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629672</v>
+        <v>629653</v>
       </c>
       <c r="R3" t="n">
-        <v>6918466</v>
+        <v>6918484</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127780507</v>
+        <v>127780596</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -917,7 +907,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629653</v>
+        <v>629700</v>
       </c>
       <c r="R4" t="n">
-        <v>6918484</v>
+        <v>6918458</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,6 +952,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,37 +983,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127780596</v>
+        <v>127781134</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629700</v>
+        <v>629600</v>
       </c>
       <c r="R5" t="n">
-        <v>6918458</v>
+        <v>6918449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,7 +1094,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127782134</v>
+        <v>127780867</v>
       </c>
       <c r="B6" t="n">
         <v>98470</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629724</v>
+        <v>629672</v>
       </c>
       <c r="R6" t="n">
-        <v>6918393</v>
+        <v>6918466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127782007</v>
+        <v>127780756</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>92642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,26 +2332,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2360,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629724</v>
+        <v>629700</v>
       </c>
       <c r="R18" t="n">
-        <v>6918393</v>
+        <v>6918458</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127780756</v>
+        <v>127780806</v>
       </c>
       <c r="B19" t="n">
-        <v>92642</v>
+        <v>97347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,43 +2438,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629700</v>
+        <v>629705</v>
       </c>
       <c r="R19" t="n">
-        <v>6918458</v>
+        <v>6918478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127780806</v>
+        <v>127782007</v>
       </c>
       <c r="B20" t="n">
-        <v>97347</v>
+        <v>98504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,34 +2535,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629705</v>
+        <v>629724</v>
       </c>
       <c r="R20" t="n">
-        <v>6918478</v>
+        <v>6918393</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -675,37 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127782134</v>
+        <v>127781134</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>92650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629724</v>
+        <v>629600</v>
       </c>
       <c r="R2" t="n">
-        <v>6918393</v>
+        <v>6918449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127780507</v>
+        <v>127782134</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -815,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629653</v>
+        <v>629724</v>
       </c>
       <c r="R3" t="n">
-        <v>6918484</v>
+        <v>6918393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127780596</v>
+        <v>127780867</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -916,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629700</v>
+        <v>629672</v>
       </c>
       <c r="R4" t="n">
-        <v>6918458</v>
+        <v>6918466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,11 +962,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,32 +988,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127781134</v>
+        <v>127780507</v>
       </c>
       <c r="B5" t="n">
-        <v>92642</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1016,21 +1021,16 @@
           <t>4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629600</v>
+        <v>629653</v>
       </c>
       <c r="R5" t="n">
-        <v>6918449</v>
+        <v>6918484</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127780867</v>
+        <v>127780596</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,7 +1119,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629672</v>
+        <v>629700</v>
       </c>
       <c r="R6" t="n">
-        <v>6918466</v>
+        <v>6918458</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,7 +1198,7 @@
         <v>127781923</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127780189</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>127780169</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>127781223</v>
       </c>
       <c r="B10" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>127781967</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>127780755</v>
       </c>
       <c r="B12" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>127782245</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>127780499</v>
       </c>
       <c r="B14" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>127781874</v>
       </c>
       <c r="B15" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>127780922</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>127780373</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>127780756</v>
       </c>
       <c r="B18" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127780806</v>
+        <v>127782007</v>
       </c>
       <c r="B19" t="n">
-        <v>97347</v>
+        <v>98512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,34 +2438,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629705</v>
+        <v>629724</v>
       </c>
       <c r="R19" t="n">
-        <v>6918478</v>
+        <v>6918393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127782007</v>
+        <v>127780806</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>97355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,38 +2539,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629724</v>
+        <v>629705</v>
       </c>
       <c r="R20" t="n">
-        <v>6918393</v>
+        <v>6918478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
         <v>127780668</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>127780876</v>
       </c>
       <c r="B22" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>127782100</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>127781080</v>
       </c>
       <c r="B24" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>127781827</v>
       </c>
       <c r="B25" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>127781136</v>
       </c>
       <c r="B26" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>127780720</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>127781281</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>127780808</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>127780881</v>
       </c>
       <c r="B30" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>127781736</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127781134</v>
       </c>
       <c r="B2" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>127782134</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127780867</v>
+        <v>127780507</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629672</v>
+        <v>629653</v>
       </c>
       <c r="R4" t="n">
-        <v>6918466</v>
+        <v>6918484</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,10 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127780507</v>
+        <v>127780596</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629653</v>
+        <v>629700</v>
       </c>
       <c r="R5" t="n">
-        <v>6918484</v>
+        <v>6918458</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,6 +1063,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127780596</v>
+        <v>127780867</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,7 +1124,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629700</v>
+        <v>629672</v>
       </c>
       <c r="R6" t="n">
-        <v>6918458</v>
+        <v>6918466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,7 +1198,7 @@
         <v>127781923</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>127780189</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>127780169</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,42 +1498,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127781223</v>
+        <v>127781967</v>
       </c>
       <c r="B10" t="n">
-        <v>92644</v>
+        <v>98571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1542,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629600</v>
+        <v>629682</v>
       </c>
       <c r="R10" t="n">
-        <v>6918449</v>
+        <v>6918424</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,6 +1573,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kan finnas mer runt om i blåbärsriset</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,37 +1604,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127781967</v>
+        <v>127781223</v>
       </c>
       <c r="B11" t="n">
-        <v>98478</v>
+        <v>92736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1643,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629682</v>
+        <v>629600</v>
       </c>
       <c r="R11" t="n">
-        <v>6918424</v>
+        <v>6918449</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,11 +1684,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kan finnas mer runt om i blåbärsriset</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,7 +1713,7 @@
         <v>127780755</v>
       </c>
       <c r="B12" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>127782245</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>127780499</v>
       </c>
       <c r="B14" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>127781874</v>
       </c>
       <c r="B15" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>127780922</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>127780373</v>
       </c>
       <c r="B17" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127780756</v>
+        <v>127780806</v>
       </c>
       <c r="B18" t="n">
-        <v>92650</v>
+        <v>97448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,43 +2332,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629700</v>
+        <v>629705</v>
       </c>
       <c r="R18" t="n">
-        <v>6918458</v>
+        <v>6918478</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127782007</v>
+        <v>127780756</v>
       </c>
       <c r="B19" t="n">
-        <v>98512</v>
+        <v>92742</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,26 +2429,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219874</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2466,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629724</v>
+        <v>629700</v>
       </c>
       <c r="R19" t="n">
-        <v>6918393</v>
+        <v>6918458</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,10 +2524,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127780806</v>
+        <v>127782007</v>
       </c>
       <c r="B20" t="n">
-        <v>97355</v>
+        <v>98605</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,34 +2535,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629705</v>
+        <v>629724</v>
       </c>
       <c r="R20" t="n">
-        <v>6918478</v>
+        <v>6918393</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127780668</v>
+        <v>127782100</v>
       </c>
       <c r="B21" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629662</v>
+        <v>629721</v>
       </c>
       <c r="R21" t="n">
-        <v>6918438</v>
+        <v>6918403</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2729,7 +2729,7 @@
         <v>127780876</v>
       </c>
       <c r="B22" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127782100</v>
+        <v>127781080</v>
       </c>
       <c r="B23" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629721</v>
+        <v>629647</v>
       </c>
       <c r="R23" t="n">
-        <v>6918403</v>
+        <v>6918478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127781080</v>
+        <v>127780668</v>
       </c>
       <c r="B24" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629647</v>
+        <v>629662</v>
       </c>
       <c r="R24" t="n">
-        <v>6918478</v>
+        <v>6918438</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3032,7 +3032,7 @@
         <v>127781827</v>
       </c>
       <c r="B25" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>127781136</v>
       </c>
       <c r="B26" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>127780720</v>
       </c>
       <c r="B27" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>127781281</v>
       </c>
       <c r="B28" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>127780808</v>
       </c>
       <c r="B29" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>127780881</v>
       </c>
       <c r="B30" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>127781736</v>
       </c>
       <c r="B31" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 37437-2025 artfynd.xlsx
+++ b/artfynd/A 37437-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127782134</v>
+        <v>127780867</v>
       </c>
       <c r="B3" t="n">
         <v>98571</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629724</v>
+        <v>629672</v>
       </c>
       <c r="R3" t="n">
-        <v>6918393</v>
+        <v>6918466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127780507</v>
+        <v>127782134</v>
       </c>
       <c r="B4" t="n">
         <v>98571</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629653</v>
+        <v>629724</v>
       </c>
       <c r="R4" t="n">
-        <v>6918484</v>
+        <v>6918393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127780596</v>
+        <v>127780507</v>
       </c>
       <c r="B5" t="n">
         <v>98571</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629700</v>
+        <v>629653</v>
       </c>
       <c r="R5" t="n">
-        <v>6918458</v>
+        <v>6918484</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,11 +1063,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,7 +1089,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127780867</v>
+        <v>127780596</v>
       </c>
       <c r="B6" t="n">
         <v>98571</v>
@@ -1124,7 +1119,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629672</v>
+        <v>629700</v>
       </c>
       <c r="R6" t="n">
-        <v>6918466</v>
+        <v>6918458</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>* möjligtvis kan det finnas fler runt omkring i blåbärsriset</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1498,37 +1498,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127781967</v>
+        <v>127781223</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>92736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1537,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629682</v>
+        <v>629600</v>
       </c>
       <c r="R10" t="n">
-        <v>6918424</v>
+        <v>6918449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,11 +1578,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Kan finnas mer runt om i blåbärsriset</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,42 +1604,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127781223</v>
+        <v>127781967</v>
       </c>
       <c r="B11" t="n">
-        <v>92736</v>
+        <v>98571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629600</v>
+        <v>629682</v>
       </c>
       <c r="R11" t="n">
-        <v>6918449</v>
+        <v>6918424</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,6 +1679,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kan finnas mer runt om i blåbärsriset</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127780806</v>
+        <v>127780756</v>
       </c>
       <c r="B18" t="n">
-        <v>97448</v>
+        <v>92742</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,34 +2332,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629705</v>
+        <v>629700</v>
       </c>
       <c r="R18" t="n">
-        <v>6918478</v>
+        <v>6918458</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127780756</v>
+        <v>127782007</v>
       </c>
       <c r="B19" t="n">
-        <v>92742</v>
+        <v>98605</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,31 +2438,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>219874</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2462,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629700</v>
+        <v>629724</v>
       </c>
       <c r="R19" t="n">
-        <v>6918458</v>
+        <v>6918393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127782007</v>
+        <v>127780806</v>
       </c>
       <c r="B20" t="n">
-        <v>98605</v>
+        <v>97448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,38 +2539,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Havstoviken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629724</v>
+        <v>629705</v>
       </c>
       <c r="R20" t="n">
-        <v>6918393</v>
+        <v>6918478</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127780881</v>
+        <v>127780500</v>
       </c>
       <c r="B30" t="n">
         <v>98571</v>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
